--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1317829457364341</v>
+        <v>0.1307692307692308</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -432,10 +432,10 @@
         <v>0.8740740740740741</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>5</v>
